--- a/Cambodia/output/CAM2313M/report.xlsx
+++ b/Cambodia/output/CAM2313M/report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t xml:space="preserve">time</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t xml:space="preserve">Utricularia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vigna</t>
   </si>
   <si>
     <t xml:space="preserve">Wolffia</t>
@@ -623,7 +626,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101.5</v>
+        <v>0.5</v>
       </c>
       <c r="B2" t="n">
         <v>211</v>
@@ -680,7 +683,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103.5</v>
+        <v>2.5</v>
       </c>
       <c r="B3" t="n">
         <v>69</v>
@@ -707,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -728,7 +731,7 @@
         <v>238</v>
       </c>
       <c r="Q3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
         <v>39</v>
@@ -739,7 +742,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
         <v>58</v>
@@ -756,10 +759,10 @@
       <c r="H4" t="n">
         <v>34</v>
       </c>
-      <c r="I4"/>
-      <c r="J4" t="n">
-        <v>140</v>
-      </c>
+      <c r="I4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4"/>
       <c r="K4" t="n">
         <v>4</v>
       </c>
@@ -778,13 +781,13 @@
         <v>80</v>
       </c>
       <c r="R4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122.5</v>
+        <v>21.5</v>
       </c>
       <c r="B5"/>
       <c r="C5"/>
@@ -811,11 +814,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130</v>
+        <v>27.5</v>
       </c>
       <c r="B6"/>
       <c r="C6" t="n">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -826,7 +829,9 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
-      <c r="M6"/>
+      <c r="M6" t="n">
+        <v>23</v>
+      </c>
       <c r="N6"/>
       <c r="O6"/>
       <c r="P6"/>
@@ -836,11 +841,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131.5</v>
+        <v>29</v>
       </c>
       <c r="B7"/>
       <c r="C7" t="n">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -859,6 +864,56 @@
       <c r="R7"/>
       <c r="S7"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8" t="n">
+        <v>74</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1036,10 +1091,13 @@
       <c r="BC1" t="s">
         <v>72</v>
       </c>
+      <c r="BD1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101.5</v>
+        <v>0.5</v>
       </c>
       <c r="B2" t="n">
         <v>71</v>
@@ -1075,7 +1133,7 @@
         <v>186</v>
       </c>
       <c r="M2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N2" t="n">
         <v>238</v>
@@ -1114,13 +1172,13 @@
         <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AA2" t="n">
         <v>115</v>
       </c>
       <c r="AB2" t="n">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="AC2" t="n">
         <v>103</v>
@@ -1138,7 +1196,7 @@
         <v>64</v>
       </c>
       <c r="AH2" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AI2" t="n">
         <v>143</v>
@@ -1196,15 +1254,18 @@
         <v>285</v>
       </c>
       <c r="BB2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC2" t="n">
         <v>55</v>
       </c>
-      <c r="BC2" t="n">
-        <v>103</v>
+      <c r="BD2" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103.5</v>
+        <v>2.5</v>
       </c>
       <c r="B3" t="n">
         <v>47</v>
@@ -1303,7 +1364,7 @@
         <v>39</v>
       </c>
       <c r="AH3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AI3" t="n">
         <v>126</v>
@@ -1347,7 +1408,7 @@
         <v>54</v>
       </c>
       <c r="AX3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AY3" t="n">
         <v>8</v>
@@ -1356,18 +1417,21 @@
         <v>33</v>
       </c>
       <c r="BA3" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="BB3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC3" t="n">
         <v>23</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BD3" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
         <v>29</v>
@@ -1388,9 +1452,7 @@
       <c r="H4" t="n">
         <v>149</v>
       </c>
-      <c r="I4" t="n">
-        <v>11</v>
-      </c>
+      <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4" t="n">
@@ -1428,7 +1490,7 @@
       </c>
       <c r="AA4"/>
       <c r="AB4" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AC4"/>
       <c r="AD4"/>
@@ -1442,21 +1504,17 @@
       <c r="AH4" t="n">
         <v>72</v>
       </c>
-      <c r="AI4" t="n">
-        <v>71</v>
-      </c>
+      <c r="AI4"/>
       <c r="AJ4"/>
       <c r="AK4" t="n">
         <v>407</v>
       </c>
-      <c r="AL4" t="n">
-        <v>113</v>
-      </c>
+      <c r="AL4"/>
       <c r="AM4" t="n">
         <v>79</v>
       </c>
       <c r="AN4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AO4" t="n">
         <v>17</v>
@@ -1492,13 +1550,16 @@
         <v>944</v>
       </c>
       <c r="BB4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC4" t="n">
         <v>7</v>
       </c>
-      <c r="BC4"/>
+      <c r="BD4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="B5"/>
       <c r="C5"/>
@@ -1536,7 +1597,7 @@
       <c r="AI5"/>
       <c r="AJ5"/>
       <c r="AK5" t="n">
-        <v>10416</v>
+        <v>10421</v>
       </c>
       <c r="AL5"/>
       <c r="AM5"/>
@@ -1556,10 +1617,11 @@
       <c r="BA5"/>
       <c r="BB5"/>
       <c r="BC5"/>
+      <c r="BD5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108.5</v>
+        <v>7.5</v>
       </c>
       <c r="B6"/>
       <c r="C6"/>
@@ -1597,7 +1659,7 @@
       <c r="AI6"/>
       <c r="AJ6"/>
       <c r="AK6" t="n">
-        <v>3638</v>
+        <v>3644</v>
       </c>
       <c r="AL6"/>
       <c r="AM6"/>
@@ -1617,10 +1679,11 @@
       <c r="BA6"/>
       <c r="BB6"/>
       <c r="BC6"/>
+      <c r="BD6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109.5</v>
+        <v>8.5</v>
       </c>
       <c r="B7"/>
       <c r="C7"/>
@@ -1658,7 +1721,7 @@
       <c r="AI7"/>
       <c r="AJ7"/>
       <c r="AK7" t="n">
-        <v>14057</v>
+        <v>14073</v>
       </c>
       <c r="AL7"/>
       <c r="AM7"/>
@@ -1678,10 +1741,11 @@
       <c r="BA7"/>
       <c r="BB7"/>
       <c r="BC7"/>
+      <c r="BD7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1739,10 +1803,11 @@
       <c r="BA8"/>
       <c r="BB8"/>
       <c r="BC8"/>
+      <c r="BD8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
@@ -1800,10 +1865,11 @@
       <c r="BA9"/>
       <c r="BB9"/>
       <c r="BC9"/>
+      <c r="BD9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115.5</v>
+        <v>14.5</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1861,14 +1927,17 @@
       <c r="BA10"/>
       <c r="BB10"/>
       <c r="BC10"/>
+      <c r="BD10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117</v>
+        <v>21.5</v>
       </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>201</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1876,13 +1945,17 @@
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
-      <c r="L11"/>
+      <c r="L11" t="n">
+        <v>133</v>
+      </c>
       <c r="M11"/>
       <c r="N11"/>
       <c r="O11"/>
       <c r="P11"/>
       <c r="Q11"/>
-      <c r="R11"/>
+      <c r="R11" t="n">
+        <v>53</v>
+      </c>
       <c r="S11"/>
       <c r="T11"/>
       <c r="U11"/>
@@ -1902,7 +1975,7 @@
       <c r="AI11"/>
       <c r="AJ11"/>
       <c r="AK11" t="n">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="AL11"/>
       <c r="AM11"/>
@@ -1922,16 +1995,15 @@
       <c r="BA11"/>
       <c r="BB11"/>
       <c r="BC11"/>
+      <c r="BD11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122.5</v>
+        <v>26</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12" t="n">
-        <v>201</v>
-      </c>
+      <c r="D12"/>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1940,16 +2012,14 @@
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M12"/>
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12"/>
       <c r="Q12"/>
-      <c r="R12" t="n">
-        <v>53</v>
-      </c>
+      <c r="R12"/>
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12"/>
@@ -1959,7 +2029,9 @@
       <c r="Y12"/>
       <c r="Z12"/>
       <c r="AA12"/>
-      <c r="AB12"/>
+      <c r="AB12" t="n">
+        <v>47</v>
+      </c>
       <c r="AC12"/>
       <c r="AD12"/>
       <c r="AE12"/>
@@ -1968,15 +2040,15 @@
       <c r="AH12"/>
       <c r="AI12"/>
       <c r="AJ12"/>
-      <c r="AK12" t="n">
-        <v>211</v>
-      </c>
+      <c r="AK12"/>
       <c r="AL12"/>
       <c r="AM12"/>
       <c r="AN12"/>
       <c r="AO12"/>
       <c r="AP12"/>
-      <c r="AQ12"/>
+      <c r="AQ12" t="n">
+        <v>272</v>
+      </c>
       <c r="AR12"/>
       <c r="AS12"/>
       <c r="AT12"/>
@@ -1987,12 +2059,15 @@
       <c r="AY12"/>
       <c r="AZ12"/>
       <c r="BA12"/>
-      <c r="BB12"/>
+      <c r="BB12" t="n">
+        <v>68</v>
+      </c>
       <c r="BC12"/>
+      <c r="BD12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127</v>
+        <v>27.5</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -2005,7 +2080,7 @@
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="M13"/>
       <c r="N13"/>
@@ -2031,15 +2106,15 @@
       <c r="AH13"/>
       <c r="AI13"/>
       <c r="AJ13"/>
-      <c r="AK13"/>
+      <c r="AK13" t="n">
+        <v>409</v>
+      </c>
       <c r="AL13"/>
       <c r="AM13"/>
       <c r="AN13"/>
       <c r="AO13"/>
       <c r="AP13"/>
-      <c r="AQ13" t="n">
-        <v>271</v>
-      </c>
+      <c r="AQ13"/>
       <c r="AR13"/>
       <c r="AS13"/>
       <c r="AT13"/>
@@ -2052,10 +2127,11 @@
       <c r="BA13"/>
       <c r="BB13"/>
       <c r="BC13"/>
+      <c r="BD13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128.5</v>
+        <v>29</v>
       </c>
       <c r="B14"/>
       <c r="C14"/>
@@ -2067,9 +2143,7 @@
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
-      <c r="L14" t="n">
-        <v>72</v>
-      </c>
+      <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
       <c r="O14"/>
@@ -2078,7 +2152,9 @@
       <c r="R14"/>
       <c r="S14"/>
       <c r="T14"/>
-      <c r="U14"/>
+      <c r="U14" t="n">
+        <v>239</v>
+      </c>
       <c r="V14"/>
       <c r="W14"/>
       <c r="X14"/>
@@ -2094,12 +2170,12 @@
       <c r="AH14"/>
       <c r="AI14"/>
       <c r="AJ14"/>
-      <c r="AK14" t="n">
-        <v>408</v>
-      </c>
+      <c r="AK14"/>
       <c r="AL14"/>
       <c r="AM14"/>
-      <c r="AN14"/>
+      <c r="AN14" t="n">
+        <v>55</v>
+      </c>
       <c r="AO14"/>
       <c r="AP14"/>
       <c r="AQ14"/>
@@ -2115,10 +2191,11 @@
       <c r="BA14"/>
       <c r="BB14"/>
       <c r="BC14"/>
+      <c r="BD14"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132.5</v>
+        <v>31.5</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -2158,7 +2235,7 @@
       <c r="AI15"/>
       <c r="AJ15"/>
       <c r="AK15" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL15"/>
       <c r="AM15"/>
@@ -2178,10 +2255,11 @@
       <c r="BA15"/>
       <c r="BB15"/>
       <c r="BC15"/>
+      <c r="BD15"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134.5</v>
+        <v>33.5</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -2239,10 +2317,11 @@
       <c r="BA16"/>
       <c r="BB16"/>
       <c r="BC16"/>
+      <c r="BD16"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -2280,7 +2359,7 @@
       <c r="AI17"/>
       <c r="AJ17"/>
       <c r="AK17" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AL17"/>
       <c r="AM17"/>
@@ -2300,10 +2379,11 @@
       <c r="BA17"/>
       <c r="BB17"/>
       <c r="BC17"/>
+      <c r="BD17"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>139.5</v>
+        <v>38.5</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
@@ -2363,17 +2443,18 @@
       <c r="BA18"/>
       <c r="BB18"/>
       <c r="BC18"/>
+      <c r="BD18"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>141.5</v>
+        <v>40.5</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
       <c r="F19" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
@@ -2424,17 +2505,18 @@
       <c r="BA19"/>
       <c r="BB19"/>
       <c r="BC19"/>
+      <c r="BD19"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>146.5</v>
+        <v>44</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20" t="n">
-        <v>833</v>
+        <v>376</v>
       </c>
       <c r="G20"/>
       <c r="H20"/>
@@ -2466,9 +2548,7 @@
       <c r="AH20"/>
       <c r="AI20"/>
       <c r="AJ20"/>
-      <c r="AK20" t="n">
-        <v>17598</v>
-      </c>
+      <c r="AK20"/>
       <c r="AL20"/>
       <c r="AM20"/>
       <c r="AN20"/>
@@ -2487,17 +2567,18 @@
       <c r="BA20"/>
       <c r="BB20"/>
       <c r="BC20"/>
+      <c r="BD20"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>148</v>
+        <v>45.5</v>
       </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
       <c r="F21" t="n">
-        <v>507</v>
+        <v>834</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
@@ -2529,12 +2610,12 @@
       <c r="AH21"/>
       <c r="AI21"/>
       <c r="AJ21"/>
-      <c r="AK21"/>
+      <c r="AK21" t="n">
+        <v>17622</v>
+      </c>
       <c r="AL21"/>
       <c r="AM21"/>
-      <c r="AN21" t="n">
-        <v>335</v>
-      </c>
+      <c r="AN21"/>
       <c r="AO21"/>
       <c r="AP21"/>
       <c r="AQ21"/>
@@ -2550,17 +2631,18 @@
       <c r="BA21"/>
       <c r="BB21"/>
       <c r="BC21"/>
+      <c r="BD21"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>149.5</v>
+        <v>47</v>
       </c>
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
       <c r="F22" t="n">
-        <v>963</v>
+        <v>509</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
@@ -2595,7 +2677,9 @@
       <c r="AK22"/>
       <c r="AL22"/>
       <c r="AM22"/>
-      <c r="AN22"/>
+      <c r="AN22" t="n">
+        <v>335</v>
+      </c>
       <c r="AO22"/>
       <c r="AP22"/>
       <c r="AQ22"/>
@@ -2611,17 +2695,18 @@
       <c r="BA22"/>
       <c r="BB22"/>
       <c r="BC22"/>
+      <c r="BD22"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>151.5</v>
+        <v>48.5</v>
       </c>
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
       <c r="F23" t="n">
-        <v>1622</v>
+        <v>963</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
@@ -2672,17 +2757,18 @@
       <c r="BA23"/>
       <c r="BB23"/>
       <c r="BC23"/>
+      <c r="BD23"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>153</v>
+        <v>50.5</v>
       </c>
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
       <c r="F24" t="n">
-        <v>5807</v>
+        <v>1625</v>
       </c>
       <c r="G24"/>
       <c r="H24"/>
@@ -2733,17 +2819,18 @@
       <c r="BA24"/>
       <c r="BB24"/>
       <c r="BC24"/>
+      <c r="BD24"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>154.5</v>
+        <v>52</v>
       </c>
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25"/>
       <c r="F25" t="n">
-        <v>10011</v>
+        <v>5810</v>
       </c>
       <c r="G25"/>
       <c r="H25"/>
@@ -2794,17 +2881,18 @@
       <c r="BA25"/>
       <c r="BB25"/>
       <c r="BC25"/>
+      <c r="BD25"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>156</v>
+        <v>53.5</v>
       </c>
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" t="n">
-        <v>14416</v>
+        <v>10024</v>
       </c>
       <c r="G26"/>
       <c r="H26"/>
@@ -2855,17 +2943,18 @@
       <c r="BA26"/>
       <c r="BB26"/>
       <c r="BC26"/>
+      <c r="BD26"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
       <c r="F27" t="n">
-        <v>9087</v>
+        <v>14429</v>
       </c>
       <c r="G27"/>
       <c r="H27"/>
@@ -2916,17 +3005,18 @@
       <c r="BA27"/>
       <c r="BB27"/>
       <c r="BC27"/>
+      <c r="BD27"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>159.5</v>
+        <v>57</v>
       </c>
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
       <c r="F28" t="n">
-        <v>3956</v>
+        <v>9092</v>
       </c>
       <c r="G28"/>
       <c r="H28"/>
@@ -2977,14 +3067,19 @@
       <c r="BA28"/>
       <c r="BB28"/>
       <c r="BC28"/>
+      <c r="BD28"/>
     </row>
     <row r="29">
-      <c r="A29"/>
+      <c r="A29" t="n">
+        <v>58.5</v>
+      </c>
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
-      <c r="F29"/>
+      <c r="F29" t="n">
+        <v>3963</v>
+      </c>
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
@@ -3014,9 +3109,7 @@
       <c r="AG29"/>
       <c r="AH29"/>
       <c r="AI29"/>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
+      <c r="AJ29"/>
       <c r="AK29"/>
       <c r="AL29"/>
       <c r="AM29"/>
@@ -3036,6 +3129,67 @@
       <c r="BA29"/>
       <c r="BB29"/>
       <c r="BC29"/>
+      <c r="BD29"/>
+    </row>
+    <row r="30">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+      <c r="S30"/>
+      <c r="T30"/>
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30"/>
+      <c r="AB30"/>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30"/>
+      <c r="AF30"/>
+      <c r="AG30"/>
+      <c r="AH30"/>
+      <c r="AI30"/>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30"/>
+      <c r="AL30"/>
+      <c r="AM30"/>
+      <c r="AN30"/>
+      <c r="AO30"/>
+      <c r="AP30"/>
+      <c r="AQ30"/>
+      <c r="AR30"/>
+      <c r="AS30"/>
+      <c r="AT30"/>
+      <c r="AU30"/>
+      <c r="AV30"/>
+      <c r="AW30"/>
+      <c r="AX30"/>
+      <c r="AY30"/>
+      <c r="AZ30"/>
+      <c r="BA30"/>
+      <c r="BB30"/>
+      <c r="BC30"/>
+      <c r="BD30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3109,7 +3263,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101.5</v>
+        <v>0.5</v>
       </c>
       <c r="B2" t="n">
         <v>0.0538128028564142</v>
@@ -3166,111 +3320,111 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103.5</v>
+        <v>2.5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0384829894032348</v>
+        <v>0.0384401114206128</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00278862242052426</v>
+        <v>0.00278551532033426</v>
       </c>
       <c r="D3" t="n">
-        <v>0.034021193530396</v>
+        <v>0.033983286908078</v>
       </c>
       <c r="E3" t="n">
-        <v>0.454545454545455</v>
+        <v>0.454038997214485</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0105967651979922</v>
+        <v>0.0105849582172702</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0435025097601785</v>
+        <v>0.0434540389972145</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0211935303959844</v>
+        <v>0.0211699164345404</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00446179587283882</v>
+        <v>0.00445682451253482</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0507529280535415</v>
+        <v>0.0512534818941504</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000557724484104852</v>
+        <v>0.000557103064066852</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0011154489682097</v>
+        <v>0.0011142061281337</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0245398773006135</v>
+        <v>0.0245125348189415</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0245398773006135</v>
+        <v>0.0245125348189415</v>
       </c>
       <c r="O3" t="n">
-        <v>0.049079754601227</v>
+        <v>0.049025069637883</v>
       </c>
       <c r="P3" t="n">
-        <v>0.132738427216955</v>
+        <v>0.132590529247911</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0552147239263804</v>
+        <v>0.0557103064066852</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0217512548800892</v>
+        <v>0.0217270194986072</v>
       </c>
       <c r="S3" t="n">
-        <v>0.030117122141662</v>
+        <v>0.03008356545961</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.076215505913272</v>
+        <v>0.0923566878980892</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0486202365308804</v>
+        <v>0.0589171974522293</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="n">
-        <v>0.346911957950066</v>
+        <v>0.420382165605096</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.0446780551905388</v>
-      </c>
-      <c r="I4"/>
-      <c r="J4" t="n">
-        <v>0.183968462549277</v>
-      </c>
+        <v>0.054140127388535</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0127388535031847</v>
+      </c>
+      <c r="J4"/>
       <c r="K4" t="n">
-        <v>0.00525624178712221</v>
+        <v>0.00636942675159236</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00394218134034166</v>
+        <v>0.00477707006369427</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0433639947437582</v>
+        <v>0.0525477707006369</v>
       </c>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.0604467805519054</v>
+        <v>0.0732484076433121</v>
       </c>
       <c r="P4"/>
       <c r="Q4" t="n">
-        <v>0.105124835742444</v>
+        <v>0.127388535031847</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0814717477003942</v>
+        <v>0.0971337579617834</v>
       </c>
       <c r="S4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122.5</v>
+        <v>21.5</v>
       </c>
       <c r="B5"/>
       <c r="C5"/>
@@ -3297,11 +3451,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130</v>
+        <v>27.5</v>
       </c>
       <c r="B6"/>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.616666666666667</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -3312,7 +3466,9 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
-      <c r="M6"/>
+      <c r="M6" t="n">
+        <v>0.383333333333333</v>
+      </c>
       <c r="N6"/>
       <c r="O6"/>
       <c r="P6"/>
@@ -3322,7 +3478,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131.5</v>
+        <v>29</v>
       </c>
       <c r="B7"/>
       <c r="C7" t="n">
@@ -3345,6 +3501,56 @@
       <c r="R7"/>
       <c r="S7"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3522,469 +3728,475 @@
       <c r="BC1" t="s">
         <v>72</v>
       </c>
+      <c r="BD1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101.5</v>
+        <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00867758494255683</v>
+        <v>0.00865431496830814</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0105108775360548</v>
+        <v>0.0104826913700634</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000733317037399169</v>
+        <v>0.000731350560702097</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0070887313615253</v>
+        <v>0.00706972208678693</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0263994133463701</v>
+        <v>0.0263286201852755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0299437790271327</v>
+        <v>0.0298634812286689</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0567098508922024</v>
+        <v>0.0565577766942955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0193106819848448</v>
+        <v>0.0192588980984885</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0162551943290149</v>
+        <v>0.0162116040955631</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0130774871669518</v>
+        <v>0.0130424183325207</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0227328281593742</v>
+        <v>0.022671867381765</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0070887313615253</v>
+        <v>0.00719161384690395</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0290882424835004</v>
+        <v>0.0290102389078498</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00659985333659252</v>
+        <v>0.00658215504631887</v>
       </c>
       <c r="P2" t="n">
-        <v>0.010021999511122</v>
+        <v>0.00999512432959532</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0123441701295527</v>
+        <v>0.0123110677718186</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0111219750672207</v>
+        <v>0.0110921501706485</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00391102419946223</v>
+        <v>0.00390053632374451</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00879980444879003</v>
+        <v>0.00877620672842516</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00684429234905891</v>
+        <v>0.0068259385665529</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00329992666829626</v>
+        <v>0.00329107752315943</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0228550476656074</v>
+        <v>0.022793759141882</v>
       </c>
       <c r="X2" t="n">
-        <v>0.023221706184307</v>
+        <v>0.0231594344222331</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00672207284282572</v>
+        <v>0.00670404680643589</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0237105842092398</v>
+        <v>0.0235251097025841</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0140552432168174</v>
+        <v>0.0140175524134568</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.185651429968223</v>
+        <v>0.185275475377864</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0125886091420191</v>
+        <v>0.0125548512920527</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0277438279149352</v>
+        <v>0.0276694295465627</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.00745538988022488</v>
+        <v>0.00743539736713798</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0122219506233195</v>
+        <v>0.0121891760117016</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.00782204839892447</v>
+        <v>0.00780107264748903</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0234661451967734</v>
+        <v>0.0235251097025841</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0174773893913469</v>
+        <v>0.0174305216967333</v>
       </c>
       <c r="AJ2"/>
       <c r="AK2" t="n">
-        <v>0.00562209728672696</v>
+        <v>0.00560702096538274</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0899535565876314</v>
+        <v>0.0897123354461238</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0196773405035444</v>
+        <v>0.0196245733788396</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.00635541432412613</v>
+        <v>0.00633837152608484</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.00782204839892447</v>
+        <v>0.00780107264748903</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.00684429234905891</v>
+        <v>0.0068259385665529</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.000122219506233195</v>
+        <v>0.000121891760117016</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.00158885358103153</v>
+        <v>0.00158459288152121</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0193106819848448</v>
+        <v>0.0192588980984885</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0408213150818871</v>
+        <v>0.0407118478790834</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.0134441456856514</v>
+        <v>0.0134080936128718</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.00647763383035933</v>
+        <v>0.00646026328620185</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.00659985333659252</v>
+        <v>0.00658215504631887</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0106330970422879</v>
+        <v>0.0106045831301804</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.00892202395502322</v>
+        <v>0.00889809848854217</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.00611097531165974</v>
+        <v>0.0060945880058508</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0348325592764605</v>
+        <v>0.0347391516333496</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.00672207284282572</v>
+        <v>0.00231594344222331</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0125886091420191</v>
+        <v>0.00670404680643589</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.0126767430521697</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103.5</v>
+        <v>2.5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0111718564297599</v>
+        <v>0.0111348021795783</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0137865462324697</v>
+        <v>0.013740819710969</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00166389351081531</v>
+        <v>0.00165837479270315</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009270263845971</v>
+        <v>0.00923951670220327</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0406465414784882</v>
+        <v>0.0405117270788913</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0242453054433088</v>
+        <v>0.0241648898365316</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0634656524839553</v>
+        <v>0.0632551528073916</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00261468980270977</v>
+        <v>0.00260601753139067</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00166389351081531</v>
+        <v>0.00165837479270315</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003090087948657</v>
+        <v>0.00307983890073442</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0285238887568338</v>
+        <v>0.0284292821606254</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0125980508676016</v>
+        <v>0.0125562662876096</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00451628238649869</v>
+        <v>0.0045013030087657</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00879486570002377</v>
+        <v>0.00876569533285951</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00404088424055146</v>
+        <v>0.00402748163942194</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0228191110054671</v>
+        <v>0.0227434257285004</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0202044212027573</v>
+        <v>0.0201374081971097</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0183028286189684</v>
+        <v>0.0182421227197347</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00237699072973615</v>
+        <v>0.00236910684671879</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00903256477299738</v>
+        <v>0.00900260601753139</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00451628238649869</v>
+        <v>0.0045013030087657</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0301877822676492</v>
+        <v>0.0300876569533286</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0213929165676254</v>
+        <v>0.0213219616204691</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000237699072973615</v>
+        <v>0.000236910684671879</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0354171618730687</v>
+        <v>0.0352996920161099</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0106964582838127</v>
+        <v>0.0106609808102345</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0815307820299501</v>
+        <v>0.0812603648424544</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.00237699072973615</v>
+        <v>0.00236910684671879</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0313762776325172</v>
+        <v>0.031272210376688</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0102210601378655</v>
+        <v>0.0101871594408908</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0166389351081531</v>
+        <v>0.0165837479270315</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.009270263845971</v>
+        <v>0.00923951670220327</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0444497266460661</v>
+        <v>0.0445392087183132</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0299500831946755</v>
+        <v>0.0298507462686567</v>
       </c>
       <c r="AJ3"/>
       <c r="AK3" t="n">
-        <v>0.00332778702163062</v>
+        <v>0.0033167495854063</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.074162110767768</v>
+        <v>0.0739161336176262</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0501545043974329</v>
+        <v>0.0499881544657664</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.00879486570002377</v>
+        <v>0.00876569533285951</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.00380318516757785</v>
+        <v>0.00379057095475006</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.00974566199191823</v>
+        <v>0.00971333807154703</v>
       </c>
       <c r="AQ3"/>
       <c r="AR3" t="n">
-        <v>0.000950796291894462</v>
+        <v>0.000947642738687515</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0244830045162824</v>
+        <v>0.0244018005212035</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0320893748514381</v>
+        <v>0.0319829424307036</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0149750415973378</v>
+        <v>0.0149253731343284</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0183028286189684</v>
+        <v>0.0182421227197347</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0128357499405752</v>
+        <v>0.0127931769722814</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0128357499405752</v>
+        <v>0.0130300876569533</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.00190159258378892</v>
+        <v>0.00189528547737503</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.00784406940812931</v>
+        <v>0.007818052594172</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0670311385785595</v>
+        <v>0.0665719023927979</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.00546707867839315</v>
+        <v>0.00307983890073442</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0202044212027573</v>
+        <v>0.00544894574745321</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.0201374081971097</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0089922480620155</v>
+        <v>0.00950508030154048</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00496124031007752</v>
+        <v>0.00524418223533268</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000310077519379845</v>
+        <v>0.000327761389708292</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0186046511627907</v>
+        <v>0.0196656833824975</v>
       </c>
       <c r="F4"/>
       <c r="G4" t="n">
-        <v>0.0207751937984496</v>
+        <v>0.0219600131104556</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0462015503875969</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.00341085271317829</v>
-      </c>
+        <v>0.0488364470665356</v>
+      </c>
+      <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4" t="n">
-        <v>0.0356589147286822</v>
+        <v>0.0376925598164536</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0114728682170543</v>
+        <v>0.0121271714192068</v>
       </c>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.00496124031007752</v>
+        <v>0.00524418223533268</v>
       </c>
       <c r="P4"/>
       <c r="Q4"/>
       <c r="R4" t="n">
-        <v>0.0142635658914729</v>
+        <v>0.0150770239265814</v>
       </c>
       <c r="S4"/>
       <c r="T4" t="n">
-        <v>0.00155038759689922</v>
+        <v>0.00163880694854146</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00775193798449612</v>
+        <v>0.00819403474270731</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0747286821705426</v>
+        <v>0.0789904949196985</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0431007751937985</v>
+        <v>0.0455588331694526</v>
       </c>
       <c r="X4"/>
       <c r="Y4"/>
       <c r="Z4" t="n">
-        <v>0.0089922480620155</v>
+        <v>0.00950508030154048</v>
       </c>
       <c r="AA4"/>
       <c r="AB4" t="n">
-        <v>0.0592248062015504</v>
+        <v>0.0629301868239921</v>
       </c>
       <c r="AC4"/>
       <c r="AD4"/>
       <c r="AE4"/>
       <c r="AF4" t="n">
-        <v>0.012093023255814</v>
+        <v>0.0127826941986234</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.00434108527131783</v>
+        <v>0.00458865945591609</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0223255813953488</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.022015503875969</v>
-      </c>
+        <v>0.023598820058997</v>
+      </c>
+      <c r="AI4"/>
       <c r="AJ4"/>
       <c r="AK4" t="n">
-        <v>0.126201550387597</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.0350387596899225</v>
-      </c>
+        <v>0.133398885611275</v>
+      </c>
+      <c r="AL4"/>
       <c r="AM4" t="n">
-        <v>0.0244961240310078</v>
+        <v>0.0258931497869551</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0102325581395349</v>
+        <v>0.0111438872500819</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.00527131782945736</v>
+        <v>0.00557194362504097</v>
       </c>
       <c r="AP4"/>
       <c r="AQ4" t="n">
-        <v>0.00155038759689922</v>
+        <v>0.00163880694854146</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0291472868217054</v>
+        <v>0.0308095706325795</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0189147286821705</v>
+        <v>0.0199934447722058</v>
       </c>
       <c r="AT4"/>
       <c r="AU4" t="n">
-        <v>0.0062015503875969</v>
+        <v>0.00655522779416585</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.00310077519379845</v>
+        <v>0.00327761389708292</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.00713178294573643</v>
+        <v>0.00753851196329072</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0111627906976744</v>
+        <v>0.0117994100294985</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.000930232558139535</v>
+        <v>0.000983284169124877</v>
       </c>
       <c r="AZ4"/>
       <c r="BA4" t="n">
-        <v>0.292713178294574</v>
+        <v>0.309406751884628</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.00217054263565891</v>
-      </c>
-      <c r="BC4"/>
+        <v>0.00622746640445756</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.00229432972795805</v>
+      </c>
+      <c r="BD4"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="B5"/>
       <c r="C5"/>
@@ -4042,10 +4254,11 @@
       <c r="BA5"/>
       <c r="BB5"/>
       <c r="BC5"/>
+      <c r="BD5"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108.5</v>
+        <v>7.5</v>
       </c>
       <c r="B6"/>
       <c r="C6"/>
@@ -4103,10 +4316,11 @@
       <c r="BA6"/>
       <c r="BB6"/>
       <c r="BC6"/>
+      <c r="BD6"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109.5</v>
+        <v>8.5</v>
       </c>
       <c r="B7"/>
       <c r="C7"/>
@@ -4164,10 +4378,11 @@
       <c r="BA7"/>
       <c r="BB7"/>
       <c r="BC7"/>
+      <c r="BD7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -4225,10 +4440,11 @@
       <c r="BA8"/>
       <c r="BB8"/>
       <c r="BC8"/>
+      <c r="BD8"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
@@ -4286,10 +4502,11 @@
       <c r="BA9"/>
       <c r="BB9"/>
       <c r="BC9"/>
+      <c r="BD9"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115.5</v>
+        <v>14.5</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -4347,14 +4564,17 @@
       <c r="BA10"/>
       <c r="BB10"/>
       <c r="BC10"/>
+      <c r="BD10"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117</v>
+        <v>21.5</v>
       </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>0.336120401337793</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -4362,13 +4582,17 @@
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
-      <c r="L11"/>
+      <c r="L11" t="n">
+        <v>0.222408026755853</v>
+      </c>
       <c r="M11"/>
       <c r="N11"/>
       <c r="O11"/>
       <c r="P11"/>
       <c r="Q11"/>
-      <c r="R11"/>
+      <c r="R11" t="n">
+        <v>0.088628762541806</v>
+      </c>
       <c r="S11"/>
       <c r="T11"/>
       <c r="U11"/>
@@ -4388,7 +4612,7 @@
       <c r="AI11"/>
       <c r="AJ11"/>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>0.352842809364548</v>
       </c>
       <c r="AL11"/>
       <c r="AM11"/>
@@ -4408,16 +4632,15 @@
       <c r="BA11"/>
       <c r="BB11"/>
       <c r="BC11"/>
+      <c r="BD11"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122.5</v>
+        <v>26</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12" t="n">
-        <v>0.336120401337793</v>
-      </c>
+      <c r="D12"/>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -4426,16 +4649,14 @@
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12" t="n">
-        <v>0.222408026755853</v>
+        <v>0.258620689655172</v>
       </c>
       <c r="M12"/>
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12"/>
       <c r="Q12"/>
-      <c r="R12" t="n">
-        <v>0.088628762541806</v>
-      </c>
+      <c r="R12"/>
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12"/>
@@ -4445,7 +4666,9 @@
       <c r="Y12"/>
       <c r="Z12"/>
       <c r="AA12"/>
-      <c r="AB12"/>
+      <c r="AB12" t="n">
+        <v>0.0900383141762452</v>
+      </c>
       <c r="AC12"/>
       <c r="AD12"/>
       <c r="AE12"/>
@@ -4454,15 +4677,15 @@
       <c r="AH12"/>
       <c r="AI12"/>
       <c r="AJ12"/>
-      <c r="AK12" t="n">
-        <v>0.352842809364548</v>
-      </c>
+      <c r="AK12"/>
       <c r="AL12"/>
       <c r="AM12"/>
       <c r="AN12"/>
       <c r="AO12"/>
       <c r="AP12"/>
-      <c r="AQ12"/>
+      <c r="AQ12" t="n">
+        <v>0.521072796934866</v>
+      </c>
       <c r="AR12"/>
       <c r="AS12"/>
       <c r="AT12"/>
@@ -4473,12 +4696,15 @@
       <c r="AY12"/>
       <c r="AZ12"/>
       <c r="BA12"/>
-      <c r="BB12"/>
+      <c r="BB12" t="n">
+        <v>0.130268199233716</v>
+      </c>
       <c r="BC12"/>
+      <c r="BD12"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127</v>
+        <v>27.5</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -4491,7 +4717,7 @@
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13" t="n">
-        <v>0.332512315270936</v>
+        <v>0.14968814968815</v>
       </c>
       <c r="M13"/>
       <c r="N13"/>
@@ -4517,15 +4743,15 @@
       <c r="AH13"/>
       <c r="AI13"/>
       <c r="AJ13"/>
-      <c r="AK13"/>
+      <c r="AK13" t="n">
+        <v>0.85031185031185</v>
+      </c>
       <c r="AL13"/>
       <c r="AM13"/>
       <c r="AN13"/>
       <c r="AO13"/>
       <c r="AP13"/>
-      <c r="AQ13" t="n">
-        <v>0.667487684729064</v>
-      </c>
+      <c r="AQ13"/>
       <c r="AR13"/>
       <c r="AS13"/>
       <c r="AT13"/>
@@ -4538,10 +4764,11 @@
       <c r="BA13"/>
       <c r="BB13"/>
       <c r="BC13"/>
+      <c r="BD13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128.5</v>
+        <v>29</v>
       </c>
       <c r="B14"/>
       <c r="C14"/>
@@ -4553,9 +4780,7 @@
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
-      <c r="L14" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
       <c r="O14"/>
@@ -4564,7 +4789,9 @@
       <c r="R14"/>
       <c r="S14"/>
       <c r="T14"/>
-      <c r="U14"/>
+      <c r="U14" t="n">
+        <v>0.812925170068027</v>
+      </c>
       <c r="V14"/>
       <c r="W14"/>
       <c r="X14"/>
@@ -4580,12 +4807,12 @@
       <c r="AH14"/>
       <c r="AI14"/>
       <c r="AJ14"/>
-      <c r="AK14" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="AK14"/>
       <c r="AL14"/>
       <c r="AM14"/>
-      <c r="AN14"/>
+      <c r="AN14" t="n">
+        <v>0.187074829931973</v>
+      </c>
       <c r="AO14"/>
       <c r="AP14"/>
       <c r="AQ14"/>
@@ -4601,10 +4828,11 @@
       <c r="BA14"/>
       <c r="BB14"/>
       <c r="BC14"/>
+      <c r="BD14"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132.5</v>
+        <v>31.5</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -4633,7 +4861,7 @@
       <c r="Z15"/>
       <c r="AA15"/>
       <c r="AB15" t="n">
-        <v>0.246794871794872</v>
+        <v>0.246006389776358</v>
       </c>
       <c r="AC15"/>
       <c r="AD15"/>
@@ -4644,7 +4872,7 @@
       <c r="AI15"/>
       <c r="AJ15"/>
       <c r="AK15" t="n">
-        <v>0.753205128205128</v>
+        <v>0.753993610223642</v>
       </c>
       <c r="AL15"/>
       <c r="AM15"/>
@@ -4664,10 +4892,11 @@
       <c r="BA15"/>
       <c r="BB15"/>
       <c r="BC15"/>
+      <c r="BD15"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134.5</v>
+        <v>33.5</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -4725,10 +4954,11 @@
       <c r="BA16"/>
       <c r="BB16"/>
       <c r="BC16"/>
+      <c r="BD16"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -4786,10 +5016,11 @@
       <c r="BA17"/>
       <c r="BB17"/>
       <c r="BC17"/>
+      <c r="BD17"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>139.5</v>
+        <v>38.5</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
@@ -4849,10 +5080,11 @@
       <c r="BA18"/>
       <c r="BB18"/>
       <c r="BC18"/>
+      <c r="BD18"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>141.5</v>
+        <v>40.5</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -4910,17 +5142,18 @@
       <c r="BA19"/>
       <c r="BB19"/>
       <c r="BC19"/>
+      <c r="BD19"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>146.5</v>
+        <v>44</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20" t="n">
-        <v>0.0451955943790353</v>
+        <v>1</v>
       </c>
       <c r="G20"/>
       <c r="H20"/>
@@ -4952,9 +5185,7 @@
       <c r="AH20"/>
       <c r="AI20"/>
       <c r="AJ20"/>
-      <c r="AK20" t="n">
-        <v>0.954804405620965</v>
-      </c>
+      <c r="AK20"/>
       <c r="AL20"/>
       <c r="AM20"/>
       <c r="AN20"/>
@@ -4973,17 +5204,18 @@
       <c r="BA20"/>
       <c r="BB20"/>
       <c r="BC20"/>
+      <c r="BD20"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>148</v>
+        <v>45.5</v>
       </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
       <c r="F21" t="n">
-        <v>0.602137767220903</v>
+        <v>0.0451885565669701</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
@@ -5015,12 +5247,12 @@
       <c r="AH21"/>
       <c r="AI21"/>
       <c r="AJ21"/>
-      <c r="AK21"/>
+      <c r="AK21" t="n">
+        <v>0.95481144343303</v>
+      </c>
       <c r="AL21"/>
       <c r="AM21"/>
-      <c r="AN21" t="n">
-        <v>0.397862232779097</v>
-      </c>
+      <c r="AN21"/>
       <c r="AO21"/>
       <c r="AP21"/>
       <c r="AQ21"/>
@@ -5036,17 +5268,18 @@
       <c r="BA21"/>
       <c r="BB21"/>
       <c r="BC21"/>
+      <c r="BD21"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>149.5</v>
+        <v>47</v>
       </c>
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.603080568720379</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
@@ -5081,7 +5314,9 @@
       <c r="AK22"/>
       <c r="AL22"/>
       <c r="AM22"/>
-      <c r="AN22"/>
+      <c r="AN22" t="n">
+        <v>0.396919431279621</v>
+      </c>
       <c r="AO22"/>
       <c r="AP22"/>
       <c r="AQ22"/>
@@ -5097,10 +5332,11 @@
       <c r="BA22"/>
       <c r="BB22"/>
       <c r="BC22"/>
+      <c r="BD22"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>151.5</v>
+        <v>48.5</v>
       </c>
       <c r="B23"/>
       <c r="C23"/>
@@ -5158,10 +5394,11 @@
       <c r="BA23"/>
       <c r="BB23"/>
       <c r="BC23"/>
+      <c r="BD23"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>153</v>
+        <v>50.5</v>
       </c>
       <c r="B24"/>
       <c r="C24"/>
@@ -5219,10 +5456,11 @@
       <c r="BA24"/>
       <c r="BB24"/>
       <c r="BC24"/>
+      <c r="BD24"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>154.5</v>
+        <v>52</v>
       </c>
       <c r="B25"/>
       <c r="C25"/>
@@ -5280,10 +5518,11 @@
       <c r="BA25"/>
       <c r="BB25"/>
       <c r="BC25"/>
+      <c r="BD25"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>156</v>
+        <v>53.5</v>
       </c>
       <c r="B26"/>
       <c r="C26"/>
@@ -5341,10 +5580,11 @@
       <c r="BA26"/>
       <c r="BB26"/>
       <c r="BC26"/>
+      <c r="BD26"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
@@ -5402,10 +5642,11 @@
       <c r="BA27"/>
       <c r="BB27"/>
       <c r="BC27"/>
+      <c r="BD27"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>159.5</v>
+        <v>57</v>
       </c>
       <c r="B28"/>
       <c r="C28"/>
@@ -5463,14 +5704,19 @@
       <c r="BA28"/>
       <c r="BB28"/>
       <c r="BC28"/>
+      <c r="BD28"/>
     </row>
     <row r="29">
-      <c r="A29"/>
+      <c r="A29" t="n">
+        <v>58.5</v>
+      </c>
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
-      <c r="F29"/>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
@@ -5500,9 +5746,7 @@
       <c r="AG29"/>
       <c r="AH29"/>
       <c r="AI29"/>
-      <c r="AJ29" t="e">
-        <v>#NUM!</v>
-      </c>
+      <c r="AJ29"/>
       <c r="AK29"/>
       <c r="AL29"/>
       <c r="AM29"/>
@@ -5522,6 +5766,67 @@
       <c r="BA29"/>
       <c r="BB29"/>
       <c r="BC29"/>
+      <c r="BD29"/>
+    </row>
+    <row r="30">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+      <c r="S30"/>
+      <c r="T30"/>
+      <c r="U30"/>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30"/>
+      <c r="AB30"/>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30"/>
+      <c r="AF30"/>
+      <c r="AG30"/>
+      <c r="AH30"/>
+      <c r="AI30"/>
+      <c r="AJ30" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AK30"/>
+      <c r="AL30"/>
+      <c r="AM30"/>
+      <c r="AN30"/>
+      <c r="AO30"/>
+      <c r="AP30"/>
+      <c r="AQ30"/>
+      <c r="AR30"/>
+      <c r="AS30"/>
+      <c r="AT30"/>
+      <c r="AU30"/>
+      <c r="AV30"/>
+      <c r="AW30"/>
+      <c r="AX30"/>
+      <c r="AY30"/>
+      <c r="AZ30"/>
+      <c r="BA30"/>
+      <c r="BB30"/>
+      <c r="BC30"/>
+      <c r="BD30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
